--- a/plots/Tables_T1-T8.xlsx
+++ b/plots/Tables_T1-T8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elwel\OneDrive\Desktop\aquatic_data\git\BOSCH\plots\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40436072c29b51f3/University of Johannesburg/Post-Doc/Size-Temperature Changes/BOSCH/plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9BBA78-DC42-420A-8FB4-F0527796B7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{FA9BBA78-DC42-420A-8FB4-F0527796B7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC67167-0FFC-4A88-8510-F06A406DC5E9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="4" xr2:uid="{F8FC7950-181F-4A0A-89C3-A717DF6795FB}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="8" xr2:uid="{F8FC7950-181F-4A0A-89C3-A717DF6795FB}"/>
   </bookViews>
   <sheets>
     <sheet name="T1_drymassYr" sheetId="7" r:id="rId1"/>
@@ -21,13 +21,14 @@
     <sheet name="T6_bodyLengthTemp" sheetId="5" r:id="rId6"/>
     <sheet name="T7_headTemp" sheetId="6" r:id="rId7"/>
     <sheet name="T8_otherTemp" sheetId="1" r:id="rId8"/>
+    <sheet name="T9_lengthMassEquations" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="300">
   <si>
     <t>Species</t>
   </si>
@@ -114,6 +115,1027 @@
   </si>
   <si>
     <t>Temperature</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>log10(a)</t>
+  </si>
+  <si>
+    <t>Oreodytes sanmarkii</t>
+  </si>
+  <si>
+    <t>Smock, 1980</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/j.1365-2427.1980.tb01211.x</t>
+  </si>
+  <si>
+    <t>genus</t>
+  </si>
+  <si>
+    <t>Hydroprous spp. (Adult)</t>
+  </si>
+  <si>
+    <t>mg</t>
+  </si>
+  <si>
+    <t>M = EXP(LN(a) + b * LN(L))</t>
+  </si>
+  <si>
+    <t>Hydraena minutissima</t>
+  </si>
+  <si>
+    <t>Benke et al., 1999</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.2307/1468447</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>Hydraena dentipes</t>
+  </si>
+  <si>
+    <t>Hydraena sp.</t>
+  </si>
+  <si>
+    <t>Hydraena gracilis</t>
+  </si>
+  <si>
+    <t>Esolus parallelepipedus</t>
+  </si>
+  <si>
+    <t>family</t>
+  </si>
+  <si>
+    <t>Anacaena lutescens</t>
+  </si>
+  <si>
+    <t>log10(DM) = log10(a) + b(log10(L))</t>
+  </si>
+  <si>
+    <t>Silo sp.</t>
+  </si>
+  <si>
+    <t>Nemoura sp.</t>
+  </si>
+  <si>
+    <t>Amphinemura sp.</t>
+  </si>
+  <si>
+    <t>Limnius volckmari</t>
+  </si>
+  <si>
+    <t>Psychomyia pusilla</t>
+  </si>
+  <si>
+    <t>Beraeodes minutus</t>
+  </si>
+  <si>
+    <t>M = a(L^b)</t>
+  </si>
+  <si>
+    <t>Micrasema longulum</t>
+  </si>
+  <si>
+    <t>Micrasema minimum</t>
+  </si>
+  <si>
+    <t>Limnius perrisi</t>
+  </si>
+  <si>
+    <t>Dixa sp.</t>
+  </si>
+  <si>
+    <t>Adicella reducta</t>
+  </si>
+  <si>
+    <t>Habrophlebia lauta</t>
+  </si>
+  <si>
+    <t>Elmis aenea/maugetii/rietscheli/rioloides</t>
+  </si>
+  <si>
+    <t>Agapetus sp.</t>
+  </si>
+  <si>
+    <t>Pisidium sp.</t>
+  </si>
+  <si>
+    <t>Hornbach et al., 1996</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/02705060.1996.9663483</t>
+  </si>
+  <si>
+    <t>DM = a(L^b)</t>
+  </si>
+  <si>
+    <t>Torleya major</t>
+  </si>
+  <si>
+    <t>Baetis fuscatus/scambus</t>
+  </si>
+  <si>
+    <t>Anomalopterygella chauviniana</t>
+  </si>
+  <si>
+    <t>Silo nigricornis</t>
+  </si>
+  <si>
+    <t>Glossosoma sp.</t>
+  </si>
+  <si>
+    <t>Silo piceus</t>
+  </si>
+  <si>
+    <t>Baetis vernus</t>
+  </si>
+  <si>
+    <t>Leptophlebia marginata</t>
+  </si>
+  <si>
+    <t>Baetis muticus</t>
+  </si>
+  <si>
+    <t>Oulimnius tuberculatus</t>
+  </si>
+  <si>
+    <t>Silo pallipes</t>
+  </si>
+  <si>
+    <t>Leptoceridae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Siphonoperla sp.</t>
+  </si>
+  <si>
+    <t>Lype reducta</t>
+  </si>
+  <si>
+    <t>Athripsodes sp.</t>
+  </si>
+  <si>
+    <t>Baetis niger</t>
+  </si>
+  <si>
+    <t>Lepidostoma basale</t>
+  </si>
+  <si>
+    <t>Leuctra nigra</t>
+  </si>
+  <si>
+    <t>Clinocerinae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Paraleptophlebia submarginata</t>
+  </si>
+  <si>
+    <t>Brachycentrus sp.</t>
+  </si>
+  <si>
+    <t>Polycelis sp.</t>
+  </si>
+  <si>
+    <t>Rhithrogena sp.</t>
+  </si>
+  <si>
+    <t>Methot et al., 2012</t>
+  </si>
+  <si>
+    <t>http://dx.doi.org/10.1899/11-120.1</t>
+  </si>
+  <si>
+    <t>Aperture width</t>
+  </si>
+  <si>
+    <t>log10DM = log10a + b[log10L]</t>
+  </si>
+  <si>
+    <t>Isoperla sp.</t>
+  </si>
+  <si>
+    <t>Polycelis nigra/tenuis</t>
+  </si>
+  <si>
+    <t>Platambus maculatus</t>
+  </si>
+  <si>
+    <t>Hygrotus sp.</t>
+  </si>
+  <si>
+    <t>Dineutes sp. (Adult)</t>
+  </si>
+  <si>
+    <t>Heptageniidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Psychodidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Drusus annulatus/biguttatus</t>
+  </si>
+  <si>
+    <t>Gyraulus albus</t>
+  </si>
+  <si>
+    <t>Sericostoma flavicorne/personatum</t>
+  </si>
+  <si>
+    <t>Ecdyonurus sp.</t>
+  </si>
+  <si>
+    <t>Ecdyonurus venosus</t>
+  </si>
+  <si>
+    <t>Calopteryx virgo</t>
+  </si>
+  <si>
+    <t>Tinodes rostocki</t>
+  </si>
+  <si>
+    <t>Hydropsyche dinarica</t>
+  </si>
+  <si>
+    <t>Hydropsyche fulvipes</t>
+  </si>
+  <si>
+    <t>Baetis sp.</t>
+  </si>
+  <si>
+    <t>Eloeophila sp.</t>
+  </si>
+  <si>
+    <t>Tipuliidae</t>
+  </si>
+  <si>
+    <t>Protonemura sp.</t>
+  </si>
+  <si>
+    <t>Odontocerum albicorne</t>
+  </si>
+  <si>
+    <t>Caenis beskidensis</t>
+  </si>
+  <si>
+    <t>Epeorus assimilis</t>
+  </si>
+  <si>
+    <t>Hydatophylax infumatus</t>
+  </si>
+  <si>
+    <t>Laccobius sp.</t>
+  </si>
+  <si>
+    <t>Haliplus sp.</t>
+  </si>
+  <si>
+    <t>species</t>
+  </si>
+  <si>
+    <t>Peltodytes sexmaculatus (Adult)</t>
+  </si>
+  <si>
+    <t>Leptophlebiidae gen. Sp.</t>
+  </si>
+  <si>
+    <t>Ecclisopteryx dalecarlica</t>
+  </si>
+  <si>
+    <t>Potamophylax sp.</t>
+  </si>
+  <si>
+    <t>Sialis fuliginosa</t>
+  </si>
+  <si>
+    <t>Gammarus sp.</t>
+  </si>
+  <si>
+    <t>Limoniidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Psychomyiidae Gen. Sp.</t>
+  </si>
+  <si>
+    <t>Empididae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Rhyacophila tristis</t>
+  </si>
+  <si>
+    <t>Glossiphonia complanata</t>
+  </si>
+  <si>
+    <t>Rosati et al., 2012</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ecss.2012.08.008</t>
+  </si>
+  <si>
+    <t>Batracobdella sp.</t>
+  </si>
+  <si>
+    <t>Hydrachnidia Gen. sp.</t>
+  </si>
+  <si>
+    <t>Mercer et al., 2001</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1017/S0954102001000219</t>
+  </si>
+  <si>
+    <t>suborder</t>
+  </si>
+  <si>
+    <t>ug</t>
+  </si>
+  <si>
+    <t>Dugesia gonocephala</t>
+  </si>
+  <si>
+    <t>Diura bicaudata</t>
+  </si>
+  <si>
+    <t>Serratella ignita</t>
+  </si>
+  <si>
+    <t>Perlodes microcephalus</t>
+  </si>
+  <si>
+    <t>Potamophylax rotundipennis</t>
+  </si>
+  <si>
+    <t>Hydraena riparia</t>
+  </si>
+  <si>
+    <t>Baetidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Galba truncatula</t>
+  </si>
+  <si>
+    <t>Eklöf et al., 2017</t>
+  </si>
+  <si>
+    <t>http://dx.doi.org/10.7717/peerj.2906</t>
+  </si>
+  <si>
+    <t>Radix balthica</t>
+  </si>
+  <si>
+    <t>Hydropsyche sp.</t>
+  </si>
+  <si>
+    <t>Limnephilidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Halesus digitatus/radiatus/tesselatus</t>
+  </si>
+  <si>
+    <t>Dinocras cephalotes</t>
+  </si>
+  <si>
+    <t>Lype sp.</t>
+  </si>
+  <si>
+    <t>Hydropsyche saxonica</t>
+  </si>
+  <si>
+    <t>Leuctra sp.</t>
+  </si>
+  <si>
+    <t>Silo nigricornis/piceus</t>
+  </si>
+  <si>
+    <t>Erpobdella sp.</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s10750-015-2526-4</t>
+  </si>
+  <si>
+    <t>Tabanidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Heptagenia sp.</t>
+  </si>
+  <si>
+    <t>Corixidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Polycelis tenuis</t>
+  </si>
+  <si>
+    <t>Baetis alpinus</t>
+  </si>
+  <si>
+    <t>Goeridae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Sphaeriidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Lumbriculidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>subclass</t>
+  </si>
+  <si>
+    <t>Oligochaeta</t>
+  </si>
+  <si>
+    <t>Stylodrilus heringianus</t>
+  </si>
+  <si>
+    <t>Sialis sp.</t>
+  </si>
+  <si>
+    <t>Enchytraeidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Hydropsyche instabilis</t>
+  </si>
+  <si>
+    <t>Brachycentrus maculatus</t>
+  </si>
+  <si>
+    <t>Hesperocorixa linnaei</t>
+  </si>
+  <si>
+    <t>Cordulegaster boltonii</t>
+  </si>
+  <si>
+    <t>Habroleptoides confusa</t>
+  </si>
+  <si>
+    <t>Calopteryx splendens</t>
+  </si>
+  <si>
+    <t>Brachyptera sp.</t>
+  </si>
+  <si>
+    <t>Ephemerella mucronata</t>
+  </si>
+  <si>
+    <t>Baetis alpinus/lutheri/melanonyx/vardarensis</t>
+  </si>
+  <si>
+    <t>Eiseniella tetraedra</t>
+  </si>
+  <si>
+    <t>Atherix ibis</t>
+  </si>
+  <si>
+    <t>Anabolia nervosa</t>
+  </si>
+  <si>
+    <t>Rhyacophila nubila</t>
+  </si>
+  <si>
+    <t>Athripsodes albifrons</t>
+  </si>
+  <si>
+    <t>Polycentropodidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Calopteryx sp.</t>
+  </si>
+  <si>
+    <t>Ephemerellidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Helophorus sp.</t>
+  </si>
+  <si>
+    <t>Sphaerium sp.</t>
+  </si>
+  <si>
+    <t>Glossiphoniidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Limnius sp.</t>
+  </si>
+  <si>
+    <t>Haplotaxis gordioides</t>
+  </si>
+  <si>
+    <t>Potamophylax cingulatus/latipennis/luctuosus</t>
+  </si>
+  <si>
+    <t>Dugesia sp.</t>
+  </si>
+  <si>
+    <t>Gammarus pulex</t>
+  </si>
+  <si>
+    <t>Dicranota sp.</t>
+  </si>
+  <si>
+    <t>Rhyacophila obliterata</t>
+  </si>
+  <si>
+    <t>Lumbricidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Hydraena britteni</t>
+  </si>
+  <si>
+    <t>Anacaena globulus</t>
+  </si>
+  <si>
+    <t>Centroptilum luteolum</t>
+  </si>
+  <si>
+    <t>Lepidostoma hirtum</t>
+  </si>
+  <si>
+    <t>Baetis lutheri</t>
+  </si>
+  <si>
+    <t>Elmis latreillei</t>
+  </si>
+  <si>
+    <t>Oecetis testacea</t>
+  </si>
+  <si>
+    <t>Brachyptera risi</t>
+  </si>
+  <si>
+    <t>Asellus aquaticus</t>
+  </si>
+  <si>
+    <t>Riolus sp.</t>
+  </si>
+  <si>
+    <t>Polycentropus sp.</t>
+  </si>
+  <si>
+    <t>Sisyra sp.</t>
+  </si>
+  <si>
+    <t>all insects</t>
+  </si>
+  <si>
+    <t>Gammarus fossarum</t>
+  </si>
+  <si>
+    <t>Brachyptera seticornis</t>
+  </si>
+  <si>
+    <t>Ecdyonurus torrentis</t>
+  </si>
+  <si>
+    <t>Niphargus sp.</t>
+  </si>
+  <si>
+    <t>Caenis sp.</t>
+  </si>
+  <si>
+    <t>Mystacides azurea</t>
+  </si>
+  <si>
+    <t>Rhithrogena savoiensis</t>
+  </si>
+  <si>
+    <t>Ecclisopteryx madida</t>
+  </si>
+  <si>
+    <t>Rhyacophila sp.</t>
+  </si>
+  <si>
+    <t>Dugesia lugubris/polychroa</t>
+  </si>
+  <si>
+    <t>Cordulegaster bidentata</t>
+  </si>
+  <si>
+    <t>Limnebius truncatellus</t>
+  </si>
+  <si>
+    <t>Hydroptila sp.</t>
+  </si>
+  <si>
+    <t>Polycentropus irroratus</t>
+  </si>
+  <si>
+    <t>Goera pilosa</t>
+  </si>
+  <si>
+    <t>Procloeon bifidum</t>
+  </si>
+  <si>
+    <t>Bithynia tentaculata</t>
+  </si>
+  <si>
+    <t>Helobdella stagnalis</t>
+  </si>
+  <si>
+    <t>Mystacides sp.</t>
+  </si>
+  <si>
+    <t>Baetis vardarensis</t>
+  </si>
+  <si>
+    <t>Potamopyrgus antipodarum</t>
+  </si>
+  <si>
+    <t>Maehrlein et al., 2016</t>
+  </si>
+  <si>
+    <t>Athripsodes cinereus</t>
+  </si>
+  <si>
+    <t>Neureclipsis bimaculata</t>
+  </si>
+  <si>
+    <t>Brachycentrus subnubilus</t>
+  </si>
+  <si>
+    <t>Heptagenia flava</t>
+  </si>
+  <si>
+    <t>Helophorus aquaticus</t>
+  </si>
+  <si>
+    <t>Atrichops crassipes</t>
+  </si>
+  <si>
+    <t>Sphaerium corneum</t>
+  </si>
+  <si>
+    <t>Nepa cinerea</t>
+  </si>
+  <si>
+    <t>Dugesia lugubris</t>
+  </si>
+  <si>
+    <t>Lype phaeopa</t>
+  </si>
+  <si>
+    <t>Hydrophilidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Erpobdella nigricollis</t>
+  </si>
+  <si>
+    <t>Erpobdella vilnensis</t>
+  </si>
+  <si>
+    <t>Heptagenia sulphurea</t>
+  </si>
+  <si>
+    <t>Erpobdellidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Erpobdella octoculata</t>
+  </si>
+  <si>
+    <t>Glyphotaelius pellucidus</t>
+  </si>
+  <si>
+    <t>Leuctra geniculata</t>
+  </si>
+  <si>
+    <t>log(M) = log(a) + b(log(L)</t>
+  </si>
+  <si>
+    <t>Limnephilus sp.</t>
+  </si>
+  <si>
+    <t>Piscicolidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Piscicola geometra</t>
+  </si>
+  <si>
+    <t>Taeniopteryx schoenemundi</t>
+  </si>
+  <si>
+    <t>Erpobdella testacea</t>
+  </si>
+  <si>
+    <t>Hemiclepsis marginata</t>
+  </si>
+  <si>
+    <t>Glossiphonia concolor</t>
+  </si>
+  <si>
+    <t>Dendrocoelum lacteum</t>
+  </si>
+  <si>
+    <t>Theromyzon tessulatum</t>
+  </si>
+  <si>
+    <t>Corbicula fluminea</t>
+  </si>
+  <si>
+    <t>Stites et al., 1995</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1139/f95-044</t>
+  </si>
+  <si>
+    <t>Sisyra terminalis</t>
+  </si>
+  <si>
+    <t>Mystacides longicornis/nigra</t>
+  </si>
+  <si>
+    <t>Stylaria lacustris</t>
+  </si>
+  <si>
+    <t>Gomphus vulgatissimus</t>
+  </si>
+  <si>
+    <t>Ophiogomphus cecilia</t>
+  </si>
+  <si>
+    <t>Viviparus viviparus</t>
+  </si>
+  <si>
+    <t>Shell height</t>
+  </si>
+  <si>
+    <t>Tipulidae Gen. sp.</t>
+  </si>
+  <si>
+    <t>Dugesia tigrina</t>
+  </si>
+  <si>
+    <t>Anodonta anatina</t>
+  </si>
+  <si>
+    <t>Cameron et al., 1979; Hanson et al., 1988</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1139/z79-217; https://doi.org/10.1139/z88-035</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Chaetopteryx villosa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ssp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Ecdyonurus venosus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-Gr.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Ecdyonurus helveticus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-Gr.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Hydropsyche pellucidula</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-Gr.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Polycentropus flavomaculatus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ssp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Athripsodes bilineatus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ssp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rhithrogena semicolorata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-Gr.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Elodes minuta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>-Gr.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Hydropsyche contubernalis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ssp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Onychogomphus forcipatus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ssp.</t>
+    </r>
+  </si>
+  <si>
+    <t>All insects</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Anodonta cataracta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Anodonta grandis simpsoniana</t>
+    </r>
+  </si>
+  <si>
+    <t>Values used</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Source DOI</t>
+  </si>
+  <si>
+    <t>Length-mass taxonomic level</t>
+  </si>
+  <si>
+    <t>Equation from source</t>
   </si>
 </sst>
 </file>
@@ -688,7 +1710,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -782,6 +1804,39 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1159,16 +2214,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5FE6C40-A2BF-4226-8872-2A85C6161F3F}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="1"/>
-    <col min="5" max="5" width="12.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="9.54296875" customWidth="1"/>
+    <col min="3" max="4" width="8.90625" style="1"/>
+    <col min="5" max="5" width="12.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1188,7 +2243,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -1212,7 +2267,7 @@
       <c r="J2" s="22"/>
       <c r="K2" s="22"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>
       <c r="B3" s="7" t="s">
         <v>10</v>
@@ -1234,7 +2289,7 @@
       <c r="J3" s="22"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="26"/>
       <c r="B4" s="7" t="s">
         <v>11</v>
@@ -1256,7 +2311,7 @@
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="27"/>
       <c r="B5" s="9" t="s">
         <v>15</v>
@@ -1278,7 +2333,7 @@
       <c r="J5" s="22"/>
       <c r="K5" s="22"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>7</v>
       </c>
@@ -1302,7 +2357,7 @@
       <c r="J6" s="22"/>
       <c r="K6" s="22"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="26"/>
       <c r="B7" s="7" t="s">
         <v>10</v>
@@ -1324,7 +2379,7 @@
       <c r="J7" s="22"/>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -1346,7 +2401,7 @@
       <c r="J8" s="22"/>
       <c r="K8" s="22"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="9" t="s">
         <v>15</v>
@@ -1368,7 +2423,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>18</v>
       </c>
@@ -1392,7 +2447,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
       <c r="B11" s="7" t="s">
         <v>10</v>
@@ -1414,7 +2469,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="7" t="s">
         <v>11</v>
@@ -1436,7 +2491,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="27"/>
       <c r="B13" s="9" t="s">
         <v>15</v>
@@ -1458,7 +2513,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="22"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>19</v>
       </c>
@@ -1482,7 +2537,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="7" t="s">
         <v>10</v>
@@ -1504,7 +2559,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="7" t="s">
         <v>11</v>
@@ -1526,7 +2581,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="22"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="27"/>
       <c r="B17" s="9" t="s">
         <v>15</v>
@@ -1548,7 +2603,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="22"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>20</v>
       </c>
@@ -1572,7 +2627,7 @@
       <c r="J18" s="22"/>
       <c r="K18" s="22"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="26"/>
       <c r="B19" s="7" t="s">
         <v>10</v>
@@ -1594,7 +2649,7 @@
       <c r="J19" s="22"/>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="26"/>
       <c r="B20" s="7" t="s">
         <v>11</v>
@@ -1616,7 +2671,7 @@
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="27"/>
       <c r="B21" s="9" t="s">
         <v>15</v>
@@ -1638,7 +2693,7 @@
       <c r="J21" s="22"/>
       <c r="K21" s="22"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
         <v>13</v>
       </c>
@@ -1662,7 +2717,7 @@
       <c r="J22" s="22"/>
       <c r="K22" s="22"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
       <c r="B23" s="7" t="s">
         <v>10</v>
@@ -1684,7 +2739,7 @@
       <c r="J23" s="22"/>
       <c r="K23" s="22"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="26"/>
       <c r="B24" s="7" t="s">
         <v>11</v>
@@ -1706,7 +2761,7 @@
       <c r="J24" s="22"/>
       <c r="K24" s="22"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="27"/>
       <c r="B25" s="9" t="s">
         <v>15</v>
@@ -1728,7 +2783,7 @@
       <c r="J25" s="22"/>
       <c r="K25" s="22"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>21</v>
       </c>
@@ -1752,7 +2807,7 @@
       <c r="J26" s="22"/>
       <c r="K26" s="22"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="26"/>
       <c r="B27" s="7" t="s">
         <v>10</v>
@@ -1774,7 +2829,7 @@
       <c r="J27" s="22"/>
       <c r="K27" s="22"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
       <c r="B28" s="7" t="s">
         <v>11</v>
@@ -1796,7 +2851,7 @@
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="27"/>
       <c r="B29" s="9" t="s">
         <v>15</v>
@@ -1818,7 +2873,7 @@
       <c r="J29" s="22"/>
       <c r="K29" s="22"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>22</v>
       </c>
@@ -1842,7 +2897,7 @@
       <c r="J30" s="22"/>
       <c r="K30" s="22"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="26"/>
       <c r="B31" s="7" t="s">
         <v>10</v>
@@ -1864,7 +2919,7 @@
       <c r="J31" s="22"/>
       <c r="K31" s="22"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="26"/>
       <c r="B32" s="7" t="s">
         <v>11</v>
@@ -1886,7 +2941,7 @@
       <c r="J32" s="22"/>
       <c r="K32" s="22"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="27"/>
       <c r="B33" s="9" t="s">
         <v>15</v>
@@ -1908,7 +2963,7 @@
       <c r="J33" s="22"/>
       <c r="K33" s="22"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="25" t="s">
         <v>23</v>
       </c>
@@ -1932,7 +2987,7 @@
       <c r="J34" s="22"/>
       <c r="K34" s="22"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="26"/>
       <c r="B35" s="7" t="s">
         <v>10</v>
@@ -1954,7 +3009,7 @@
       <c r="J35" s="22"/>
       <c r="K35" s="22"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="26"/>
       <c r="B36" s="7" t="s">
         <v>11</v>
@@ -1976,7 +3031,7 @@
       <c r="J36" s="22"/>
       <c r="K36" s="22"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="27"/>
       <c r="B37" s="9" t="s">
         <v>15</v>
@@ -2017,17 +3072,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2E2CEDA-AAF0-4B9C-9287-4ADC12013DA8}">
   <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2047,7 +3102,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -2067,7 +3122,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>
       <c r="B3" s="7" t="s">
         <v>10</v>
@@ -2085,7 +3140,7 @@
         <v>0.38200000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="26"/>
       <c r="B4" s="7" t="s">
         <v>11</v>
@@ -2103,7 +3158,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="27"/>
       <c r="B5" s="9" t="s">
         <v>15</v>
@@ -2121,7 +3176,7 @@
         <v>0.90500000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>7</v>
       </c>
@@ -2141,7 +3196,7 @@
         <v>-0.41399999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="26"/>
       <c r="B7" s="7" t="s">
         <v>10</v>
@@ -2159,7 +3214,7 @@
         <v>0.214</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -2177,7 +3232,7 @@
         <v>-1.94</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="9" t="s">
         <v>15</v>
@@ -2195,7 +3250,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>18</v>
       </c>
@@ -2215,7 +3270,7 @@
         <v>-0.52600000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
       <c r="B11" s="7" t="s">
         <v>10</v>
@@ -2233,7 +3288,7 @@
         <v>0.182</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="7" t="s">
         <v>11</v>
@@ -2251,7 +3306,7 @@
         <v>-2.883</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="27"/>
       <c r="B13" s="9" t="s">
         <v>15</v>
@@ -2269,7 +3324,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>19</v>
       </c>
@@ -2289,7 +3344,7 @@
         <v>0.36199999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="7" t="s">
         <v>10</v>
@@ -2308,7 +3363,7 @@
       </c>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="7" t="s">
         <v>11</v>
@@ -2326,7 +3381,7 @@
         <v>0.61399999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="27"/>
       <c r="B17" s="9" t="s">
         <v>15</v>
@@ -2344,7 +3399,7 @@
         <v>0.53900000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>20</v>
       </c>
@@ -2364,7 +3419,7 @@
         <v>2.7120000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="26"/>
       <c r="B19" s="7" t="s">
         <v>10</v>
@@ -2382,7 +3437,7 @@
         <v>3.8210000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="26"/>
       <c r="B20" s="7" t="s">
         <v>11</v>
@@ -2400,7 +3455,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="27"/>
       <c r="B21" s="9" t="s">
         <v>15</v>
@@ -2418,7 +3473,7 @@
         <v>0.47799999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
         <v>13</v>
       </c>
@@ -2438,7 +3493,7 @@
         <v>1.127</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
       <c r="B23" s="7" t="s">
         <v>10</v>
@@ -2456,7 +3511,7 @@
         <v>0.51700000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="26"/>
       <c r="B24" s="7" t="s">
         <v>11</v>
@@ -2474,7 +3529,7 @@
         <v>2.181</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="27"/>
       <c r="B25" s="9" t="s">
         <v>15</v>
@@ -2492,7 +3547,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>21</v>
       </c>
@@ -2512,7 +3567,7 @@
         <v>0.45900000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="26"/>
       <c r="B27" s="7" t="s">
         <v>10</v>
@@ -2530,7 +3585,7 @@
         <v>0.23100000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
       <c r="B28" s="7" t="s">
         <v>11</v>
@@ -2548,7 +3603,7 @@
         <v>1.9930000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="27"/>
       <c r="B29" s="9" t="s">
         <v>15</v>
@@ -2566,7 +3621,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>22</v>
       </c>
@@ -2586,7 +3641,7 @@
         <v>0.24199999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="26"/>
       <c r="B31" s="7" t="s">
         <v>10</v>
@@ -2604,7 +3659,7 @@
         <v>0.86499999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="26"/>
       <c r="B32" s="7" t="s">
         <v>11</v>
@@ -2622,7 +3677,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="27"/>
       <c r="B33" s="9" t="s">
         <v>15</v>
@@ -2640,7 +3695,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="25" t="s">
         <v>23</v>
       </c>
@@ -2660,7 +3715,7 @@
         <v>0.628</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="26"/>
       <c r="B35" s="7" t="s">
         <v>10</v>
@@ -2678,7 +3733,7 @@
         <v>0.20899999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="26"/>
       <c r="B36" s="7" t="s">
         <v>11</v>
@@ -2696,7 +3751,7 @@
         <v>3.0070000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="27"/>
       <c r="B37" s="9" t="s">
         <v>15</v>
@@ -2734,17 +3789,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{059F4ECD-4BBC-46D3-A403-DE87DC65F982}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2764,7 +3819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -2784,7 +3839,7 @@
         <v>-2.1556520691698201E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>
       <c r="B3" s="7" t="s">
         <v>10</v>
@@ -2802,7 +3857,7 @@
         <v>5.9441261030599497E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="26"/>
       <c r="B4" s="7" t="s">
         <v>11</v>
@@ -2820,7 +3875,7 @@
         <v>-0.36265247940485601</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="27"/>
       <c r="B5" s="9" t="s">
         <v>15</v>
@@ -2838,7 +3893,7 @@
         <v>0.71686450228000997</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
@@ -2858,7 +3913,7 @@
         <v>-3.8023410514548599E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="26"/>
       <c r="B7" s="7" t="s">
         <v>10</v>
@@ -2876,7 +3931,7 @@
         <v>2.3027602482386E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -2894,7 +3949,7 @@
         <v>-1.6512101311299401</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="9" t="s">
         <v>15</v>
@@ -2912,7 +3967,7 @@
         <v>9.8695675127376897E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>19</v>
       </c>
@@ -2932,7 +3987,7 @@
         <v>7.1595388184778702E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
       <c r="B11" s="7" t="s">
         <v>10</v>
@@ -2950,7 +4005,7 @@
         <v>4.8959408519928103E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="7" t="s">
         <v>11</v>
@@ -2968,7 +4023,7 @@
         <v>1.4623417714623099</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="27"/>
       <c r="B13" s="9" t="s">
         <v>15</v>
@@ -2986,7 +4041,7 @@
         <v>0.14364757722883201</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>20</v>
       </c>
@@ -3006,7 +4061,7 @@
         <v>0.70638064495817898</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="7" t="s">
         <v>10</v>
@@ -3024,7 +4079,7 @@
         <v>0.184539635247399</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="7" t="s">
         <v>11</v>
@@ -3042,7 +4097,7 @@
         <v>3.8277990742269701</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="27"/>
       <c r="B17" s="9" t="s">
         <v>15</v>
@@ -3060,7 +4115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>21</v>
       </c>
@@ -3080,7 +4135,7 @@
         <v>8.16041704071295E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="26"/>
       <c r="B19" s="7" t="s">
         <v>10</v>
@@ -3098,7 +4153,7 @@
         <v>2.2237132659694601E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="26"/>
       <c r="B20" s="7" t="s">
         <v>11</v>
@@ -3116,7 +4171,7 @@
         <v>3.6697253938246899</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="27"/>
       <c r="B21" s="9" t="s">
         <v>15</v>
@@ -3134,7 +4189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
         <v>22</v>
       </c>
@@ -3154,7 +4209,7 @@
         <v>8.9833901223784596E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
       <c r="B23" s="7" t="s">
         <v>10</v>
@@ -3172,7 +4227,7 @@
         <v>7.4263001574293205E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="26"/>
       <c r="B24" s="7" t="s">
         <v>11</v>
@@ -3190,7 +4245,7 @@
         <v>1.2096723714286499</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="27"/>
       <c r="B25" s="9" t="s">
         <v>15</v>
@@ -3208,7 +4263,7 @@
         <v>0.22640463554495199</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>23</v>
       </c>
@@ -3228,7 +4283,7 @@
         <v>1.9014992067197201E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="26"/>
       <c r="B27" s="7" t="s">
         <v>10</v>
@@ -3246,7 +4301,7 @@
         <v>1.38228824804072E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
       <c r="B28" s="7" t="s">
         <v>11</v>
@@ -3264,7 +4319,7 @@
         <v>1.3756169955253199</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="27"/>
       <c r="B29" s="9" t="s">
         <v>15</v>
@@ -3299,18 +4354,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E311FA9-3E8B-4093-B71E-D360A8F756AB}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" customWidth="1"/>
-    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="7" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" customWidth="1"/>
+    <col min="4" max="4" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" customWidth="1"/>
+    <col min="7" max="7" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -3333,7 +4388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
         <v>7</v>
       </c>
@@ -3356,7 +4411,7 @@
         <v>-0.23999272494990101</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="29"/>
       <c r="B3" s="32"/>
       <c r="C3" s="19" t="s">
@@ -3375,7 +4430,7 @@
         <v>0.15478753545384499</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="29"/>
       <c r="B4" s="32"/>
       <c r="C4" s="19" t="s">
@@ -3394,7 +4449,7 @@
         <v>-1.55046544443149</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="29"/>
       <c r="B5" s="33"/>
       <c r="C5" s="20" t="s">
@@ -3413,7 +4468,7 @@
         <v>0.12102984125404</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="29"/>
       <c r="B6" s="31" t="s">
         <v>12</v>
@@ -3434,7 +4489,7 @@
         <v>-0.21800427661584801</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="29"/>
       <c r="B7" s="32"/>
       <c r="C7" s="19" t="s">
@@ -3453,7 +4508,7 @@
         <v>0.111920830536785</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="29"/>
       <c r="B8" s="32"/>
       <c r="C8" s="19" t="s">
@@ -3472,7 +4527,7 @@
         <v>-1.94784362812781</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="30"/>
       <c r="B9" s="33"/>
       <c r="C9" s="20" t="s">
@@ -3491,7 +4546,7 @@
         <v>5.1433676665443101E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
         <v>13</v>
       </c>
@@ -3514,7 +4569,7 @@
         <v>8.6678506039181202E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="29"/>
       <c r="B11" s="32"/>
       <c r="C11" s="19" t="s">
@@ -3533,7 +4588,7 @@
         <v>0.73311968210265799</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="29"/>
       <c r="B12" s="32"/>
       <c r="C12" s="19" t="s">
@@ -3552,7 +4607,7 @@
         <v>0.118232408916616</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="30"/>
       <c r="B13" s="33"/>
       <c r="C13" s="20" t="s">
@@ -3586,16 +4641,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF3E8C7-42C4-45F9-B012-54B534EE367A}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="2" max="2" width="9.90625" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="8" max="11" width="8.88671875" style="19"/>
+    <col min="8" max="11" width="8.90625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3615,7 +4670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -3639,7 +4694,7 @@
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>
       <c r="B3" s="7" t="s">
         <v>10</v>
@@ -3661,7 +4716,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="26"/>
       <c r="B4" s="7" t="s">
         <v>11</v>
@@ -3683,7 +4738,7 @@
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="27"/>
       <c r="B5" s="9" t="s">
         <v>15</v>
@@ -3705,7 +4760,7 @@
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>7</v>
       </c>
@@ -3729,7 +4784,7 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="26"/>
       <c r="B7" s="7" t="s">
         <v>10</v>
@@ -3751,7 +4806,7 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -3773,7 +4828,7 @@
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="9" t="s">
         <v>15</v>
@@ -3795,7 +4850,7 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>18</v>
       </c>
@@ -3819,7 +4874,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
       <c r="B11" s="7" t="s">
         <v>10</v>
@@ -3841,7 +4896,7 @@
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="7" t="s">
         <v>11</v>
@@ -3863,7 +4918,7 @@
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="27"/>
       <c r="B13" s="9" t="s">
         <v>15</v>
@@ -3885,7 +4940,7 @@
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>19</v>
       </c>
@@ -3909,7 +4964,7 @@
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="7" t="s">
         <v>10</v>
@@ -3931,7 +4986,7 @@
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="7" t="s">
         <v>11</v>
@@ -3953,7 +5008,7 @@
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="27"/>
       <c r="B17" s="9" t="s">
         <v>15</v>
@@ -3975,7 +5030,7 @@
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>20</v>
       </c>
@@ -3999,7 +5054,7 @@
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="26"/>
       <c r="B19" s="7" t="s">
         <v>10</v>
@@ -4021,7 +5076,7 @@
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="26"/>
       <c r="B20" s="7" t="s">
         <v>11</v>
@@ -4043,7 +5098,7 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="27"/>
       <c r="B21" s="9" t="s">
         <v>15</v>
@@ -4065,7 +5120,7 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
         <v>13</v>
       </c>
@@ -4089,7 +5144,7 @@
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
       <c r="B23" s="7" t="s">
         <v>10</v>
@@ -4111,7 +5166,7 @@
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="26"/>
       <c r="B24" s="7" t="s">
         <v>11</v>
@@ -4133,7 +5188,7 @@
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="27"/>
       <c r="B25" s="9" t="s">
         <v>15</v>
@@ -4155,7 +5210,7 @@
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>21</v>
       </c>
@@ -4179,7 +5234,7 @@
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="26"/>
       <c r="B27" s="7" t="s">
         <v>10</v>
@@ -4201,7 +5256,7 @@
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
       <c r="B28" s="7" t="s">
         <v>11</v>
@@ -4223,7 +5278,7 @@
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="27"/>
       <c r="B29" s="9" t="s">
         <v>15</v>
@@ -4245,7 +5300,7 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>22</v>
       </c>
@@ -4269,7 +5324,7 @@
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="26"/>
       <c r="B31" s="7" t="s">
         <v>10</v>
@@ -4291,7 +5346,7 @@
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="26"/>
       <c r="B32" s="7" t="s">
         <v>11</v>
@@ -4313,7 +5368,7 @@
       <c r="J32" s="13"/>
       <c r="K32" s="13"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="27"/>
       <c r="B33" s="9" t="s">
         <v>15</v>
@@ -4335,7 +5390,7 @@
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="25" t="s">
         <v>23</v>
       </c>
@@ -4359,7 +5414,7 @@
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="26"/>
       <c r="B35" s="7" t="s">
         <v>10</v>
@@ -4381,7 +5436,7 @@
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="26"/>
       <c r="B36" s="7" t="s">
         <v>11</v>
@@ -4403,7 +5458,7 @@
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="27"/>
       <c r="B37" s="9" t="s">
         <v>15</v>
@@ -4444,20 +5499,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{500F118E-E1E2-4523-B1F4-E79E181278E8}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.36328125" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="11" width="8.88671875" style="21"/>
-    <col min="12" max="16384" width="8.88671875" style="2"/>
+    <col min="6" max="6" width="7.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="2"/>
+    <col min="8" max="11" width="8.90625" style="21"/>
+    <col min="12" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -4477,7 +5532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -4501,7 +5556,7 @@
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="26"/>
       <c r="B3" s="7" t="s">
         <v>10</v>
@@ -4523,7 +5578,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="7" t="s">
         <v>11</v>
@@ -4545,7 +5600,7 @@
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="27"/>
       <c r="B5" s="9" t="s">
         <v>15</v>
@@ -4567,7 +5622,7 @@
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
         <v>7</v>
       </c>
@@ -4591,7 +5646,7 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="26"/>
       <c r="B7" s="7" t="s">
         <v>10</v>
@@ -4613,7 +5668,7 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -4635,7 +5690,7 @@
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="27"/>
       <c r="B9" s="9" t="s">
         <v>15</v>
@@ -4657,7 +5712,7 @@
       <c r="J9" s="23"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="25" t="s">
         <v>18</v>
       </c>
@@ -4681,7 +5736,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="26"/>
       <c r="B11" s="7" t="s">
         <v>10</v>
@@ -4703,7 +5758,7 @@
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="26"/>
       <c r="B12" s="7" t="s">
         <v>11</v>
@@ -4725,7 +5780,7 @@
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="27"/>
       <c r="B13" s="9" t="s">
         <v>15</v>
@@ -4747,7 +5802,7 @@
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>19</v>
       </c>
@@ -4771,7 +5826,7 @@
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
       <c r="B15" s="7" t="s">
         <v>10</v>
@@ -4793,7 +5848,7 @@
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="7" t="s">
         <v>11</v>
@@ -4815,7 +5870,7 @@
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="27"/>
       <c r="B17" s="9" t="s">
         <v>15</v>
@@ -4837,7 +5892,7 @@
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
         <v>20</v>
       </c>
@@ -4861,7 +5916,7 @@
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="26"/>
       <c r="B19" s="7" t="s">
         <v>10</v>
@@ -4883,7 +5938,7 @@
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="26"/>
       <c r="B20" s="7" t="s">
         <v>11</v>
@@ -4905,7 +5960,7 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="27"/>
       <c r="B21" s="9" t="s">
         <v>15</v>
@@ -4927,7 +5982,7 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>13</v>
       </c>
@@ -4951,7 +6006,7 @@
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="26"/>
       <c r="B23" s="7" t="s">
         <v>10</v>
@@ -4973,7 +6028,7 @@
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="26"/>
       <c r="B24" s="7" t="s">
         <v>11</v>
@@ -4995,7 +6050,7 @@
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="27"/>
       <c r="B25" s="9" t="s">
         <v>15</v>
@@ -5017,7 +6072,7 @@
       <c r="J25" s="23"/>
       <c r="K25" s="13"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="25" t="s">
         <v>21</v>
       </c>
@@ -5041,7 +6096,7 @@
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="26"/>
       <c r="B27" s="7" t="s">
         <v>10</v>
@@ -5063,7 +6118,7 @@
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="26"/>
       <c r="B28" s="7" t="s">
         <v>11</v>
@@ -5085,7 +6140,7 @@
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="27"/>
       <c r="B29" s="9" t="s">
         <v>15</v>
@@ -5107,7 +6162,7 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
         <v>22</v>
       </c>
@@ -5131,7 +6186,7 @@
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="26"/>
       <c r="B31" s="7" t="s">
         <v>10</v>
@@ -5153,7 +6208,7 @@
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="26"/>
       <c r="B32" s="7" t="s">
         <v>11</v>
@@ -5175,7 +6230,7 @@
       <c r="J32" s="13"/>
       <c r="K32" s="13"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="27"/>
       <c r="B33" s="9" t="s">
         <v>15</v>
@@ -5197,7 +6252,7 @@
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="25" t="s">
         <v>23</v>
       </c>
@@ -5221,7 +6276,7 @@
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="26"/>
       <c r="B35" s="7" t="s">
         <v>10</v>
@@ -5243,7 +6298,7 @@
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="26"/>
       <c r="B36" s="7" t="s">
         <v>11</v>
@@ -5265,7 +6320,7 @@
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="27"/>
       <c r="B37" s="9" t="s">
         <v>15</v>
@@ -5306,20 +6361,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60AADF67-A8A7-4A10-9439-D84BEF17C813}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.90625" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
+    <col min="4" max="4" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.08984375" style="19" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5339,7 +6394,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -5359,7 +6414,7 @@
         <v>-3.0258641817004901E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>
       <c r="B3" s="7" t="s">
         <v>10</v>
@@ -5377,7 +6432,7 @@
         <v>5.9349795156204199E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="26"/>
       <c r="B4" s="7" t="s">
         <v>11</v>
@@ -5395,7 +6450,7 @@
         <v>-0.50983565718072599</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="27"/>
       <c r="B5" s="9" t="s">
         <v>15</v>
@@ -5413,7 +6468,7 @@
         <v>0.61016660252949695</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
@@ -5433,7 +6488,7 @@
         <v>-2.3686609511667601E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="26"/>
       <c r="B7" s="7" t="s">
         <v>10</v>
@@ -5451,7 +6506,7 @@
         <v>2.3284338438460998E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="26"/>
       <c r="B8" s="7" t="s">
         <v>11</v>
@@ -5469,7 +6524,7 @@
         <v>-1.01727646564963</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="27"/>
       <c r="B9" s="9" t="s">
         <v>15</v>
@@ -5487,7 +6542,7 @@
         <v>0.30902192898008302</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>19</v>
       </c>
@@ -5507,7 +6562,7 @@
         <v>-3.8170767973126102E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="26"/>
       <c r="B11" s="7" t="s">
         <v>10</v>
@@ -5525,7 +6580,7 @@
         <v>4.5851989913650901E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="26"/>
       <c r="B12" s="7" t="s">
         <v>11</v>
@@ -5543,7 +6598,7 @@
         <v>-0.83247789343515599</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="27"/>
       <c r="B13" s="9" t="s">
         <v>15</v>
@@ -5561,7 +6616,7 @@
         <v>0.40513925115523403</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>20</v>
       </c>
@@ -5581,7 +6636,7 @@
         <v>0.72206456453863499</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="26"/>
       <c r="B15" s="7" t="s">
         <v>10</v>
@@ -5599,7 +6654,7 @@
         <v>0.17533419508054601</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="26"/>
       <c r="B16" s="7" t="s">
         <v>11</v>
@@ -5617,7 +6672,7 @@
         <v>4.1182187205805896</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="27"/>
       <c r="B17" s="9" t="s">
         <v>15</v>
@@ -5635,7 +6690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>21</v>
       </c>
@@ -5655,7 +6710,7 @@
         <v>7.5314510026948805E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="26"/>
       <c r="B19" s="7" t="s">
         <v>10</v>
@@ -5673,7 +6728,7 @@
         <v>2.2486350338952701E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="26"/>
       <c r="B20" s="7" t="s">
         <v>11</v>
@@ -5691,7 +6746,7 @@
         <v>3.3493434413179402</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="27"/>
       <c r="B21" s="9" t="s">
         <v>15</v>
@@ -5709,7 +6764,7 @@
         <v>8.1003319641181903E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
         <v>22</v>
       </c>
@@ -5729,7 +6784,7 @@
         <v>4.9408478360734101E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
       <c r="B23" s="7" t="s">
         <v>10</v>
@@ -5747,7 +6802,7 @@
         <v>7.0109902112337197E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="26"/>
       <c r="B24" s="7" t="s">
         <v>11</v>
@@ -5765,7 +6820,7 @@
         <v>0.70472895942097902</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="27"/>
       <c r="B25" s="9" t="s">
         <v>15</v>
@@ -5783,7 +6838,7 @@
         <v>0.480978925743972</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>23</v>
       </c>
@@ -5803,7 +6858,7 @@
         <v>2.0724564636184301E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="26"/>
       <c r="B27" s="7" t="s">
         <v>10</v>
@@ -5821,7 +6876,7 @@
         <v>1.42441803107765E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
       <c r="B28" s="7" t="s">
         <v>11</v>
@@ -5839,7 +6894,7 @@
         <v>1.4549496133873701</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="27"/>
       <c r="B29" s="9" t="s">
         <v>15</v>
@@ -5874,17 +6929,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF67989-6C5A-4053-9F85-8CF60C044418}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -5907,7 +6962,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
         <v>7</v>
       </c>
@@ -5930,7 +6985,7 @@
         <v>-0.30660734542907703</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="29"/>
       <c r="B3" s="32"/>
       <c r="C3" s="19" t="s">
@@ -5949,7 +7004,7 @@
         <v>0.162411710924657</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="29"/>
       <c r="B4" s="32"/>
       <c r="C4" s="19" t="s">
@@ -5968,7 +7023,7 @@
         <v>-1.88784012977557</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="29"/>
       <c r="B5" s="33"/>
       <c r="C5" s="20" t="s">
@@ -5987,7 +7042,7 @@
         <v>5.9047416011077401E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="29"/>
       <c r="B6" s="31" t="s">
         <v>12</v>
@@ -6012,7 +7067,7 @@
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="29"/>
       <c r="B7" s="32"/>
       <c r="C7" s="19" t="s">
@@ -6035,7 +7090,7 @@
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="29"/>
       <c r="B8" s="32"/>
       <c r="C8" s="19" t="s">
@@ -6058,7 +7113,7 @@
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="30"/>
       <c r="B9" s="33"/>
       <c r="C9" s="20" t="s">
@@ -6081,7 +7136,7 @@
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
         <v>13</v>
       </c>
@@ -6108,7 +7163,7 @@
       <c r="K10" s="21"/>
       <c r="L10" s="21"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="29"/>
       <c r="B11" s="32"/>
       <c r="C11" s="19" t="s">
@@ -6127,7 +7182,7 @@
         <v>0.829295824261295</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="29"/>
       <c r="B12" s="32"/>
       <c r="C12" s="19" t="s">
@@ -6146,7 +7201,7 @@
         <v>-8.7486215484261595E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="30"/>
       <c r="B13" s="33"/>
       <c r="C13" s="20" t="s">
@@ -6175,4 +7230,6435 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC5F83C-FDFF-420F-A42C-299C3967481C}">
+  <dimension ref="A1:J225"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.08984375" style="43" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.08984375" style="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.7265625" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="4.90625" style="43" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" style="43" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.26953125" style="44" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.08984375" style="44" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.90625" style="43" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="26" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="38">
+        <v>2.5009999999999999</v>
+      </c>
+      <c r="F2" s="38">
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="G2" s="38"/>
+      <c r="H2" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F3" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G3" s="38"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F4" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G4" s="38"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F5" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G5" s="38"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F6" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G6" s="38"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F7" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G7" s="38"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F8" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G8" s="38"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F9" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G9" s="38"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="38">
+        <v>2.762</v>
+      </c>
+      <c r="F10" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G10" s="38"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="38">
+        <v>2.762</v>
+      </c>
+      <c r="F11" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G11" s="38"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F12" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G12" s="38"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="38">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="F13" s="38">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="G13" s="38"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F14" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G14" s="38"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="38">
+        <v>2.8180000000000001</v>
+      </c>
+      <c r="F15" s="38">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="G15" s="38"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="38">
+        <v>2.8180000000000001</v>
+      </c>
+      <c r="F16" s="38">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="G16" s="38"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F17" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G17" s="38"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="38">
+        <v>2.6920000000000002</v>
+      </c>
+      <c r="F18" s="38">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="G18" s="38"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F19" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G19" s="38"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="38">
+        <v>2.6859999999999999</v>
+      </c>
+      <c r="F20" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F21" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="38">
+        <v>2.9580000000000002</v>
+      </c>
+      <c r="F22" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G22" s="38"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="38">
+        <v>2.4769999999999999</v>
+      </c>
+      <c r="F23" s="38">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="38">
+        <v>2.6760000000000002</v>
+      </c>
+      <c r="F24" s="38">
+        <v>1.03E-2</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F25" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F26" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F27" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G27" s="38"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="38">
+        <v>2.9580000000000002</v>
+      </c>
+      <c r="F28" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G28" s="38"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F29" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F30" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G30" s="38"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="38">
+        <v>2.6859999999999999</v>
+      </c>
+      <c r="F31" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G31" s="38"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F32" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G32" s="38"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F33" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G33" s="38"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F34" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G34" s="38"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F35" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G35" s="38"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F36" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G36" s="38"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="38">
+        <v>2.7240000000000002</v>
+      </c>
+      <c r="F37" s="38">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="G37" s="38"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="38">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="F38" s="38">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="G38" s="38"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F39" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G39" s="38"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F40" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G40" s="38"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="38">
+        <v>2.649</v>
+      </c>
+      <c r="F41" s="38">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="G41" s="38"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="38">
+        <v>2.7189999999999999</v>
+      </c>
+      <c r="F42" s="38">
+        <v>2.8E-3</v>
+      </c>
+      <c r="G42" s="38"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="38">
+        <v>2.5459999999999998</v>
+      </c>
+      <c r="F43" s="38">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G43" s="38"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="38">
+        <v>2.6859999999999999</v>
+      </c>
+      <c r="F44" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G44" s="38"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E45" s="38">
+        <v>2.8180000000000001</v>
+      </c>
+      <c r="F45" s="38">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="G45" s="38"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F46" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G46" s="38"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F47" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G47" s="38"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="38">
+        <v>2.7</v>
+      </c>
+      <c r="F48" s="38">
+        <v>2.8840315031266047E-2</v>
+      </c>
+      <c r="G48" s="38">
+        <v>-1.54</v>
+      </c>
+      <c r="H48" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="I48" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49" s="38">
+        <v>2.742</v>
+      </c>
+      <c r="F49" s="38">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="G49" s="38"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F50" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G50" s="38"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="38">
+        <v>2.5019999999999998</v>
+      </c>
+      <c r="F51" s="38">
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="G51" s="38"/>
+      <c r="H51" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="38">
+        <v>2.5019999999999998</v>
+      </c>
+      <c r="F52" s="38">
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="G52" s="38"/>
+      <c r="H52" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I52" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J52" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="38">
+        <v>2.5859999999999999</v>
+      </c>
+      <c r="F53" s="38">
+        <v>5.3100000000000001E-2</v>
+      </c>
+      <c r="G53" s="38"/>
+      <c r="H53" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="I53" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E54" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F54" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G54" s="38"/>
+      <c r="H54" s="36"/>
+      <c r="I54" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J54" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E55" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F55" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G55" s="38"/>
+      <c r="H55" s="36"/>
+      <c r="I55" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J55" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F56" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G56" s="38"/>
+      <c r="H56" s="36"/>
+      <c r="I56" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J56" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E57" s="38">
+        <v>2.6920000000000002</v>
+      </c>
+      <c r="F57" s="38">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="G57" s="38"/>
+      <c r="H57" s="36"/>
+      <c r="I57" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E58" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F58" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G58" s="38"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J58" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C59" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D59" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F59" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G59" s="38"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J59" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C60" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" s="38">
+        <v>2.65</v>
+      </c>
+      <c r="F60" s="38">
+        <v>7.5857757502918358E-2</v>
+      </c>
+      <c r="G60" s="38">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="H60" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="I60" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J60" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E61" s="38">
+        <v>2.7410000000000001</v>
+      </c>
+      <c r="F61" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G61" s="38"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J61" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F62" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G62" s="38"/>
+      <c r="H62" s="36"/>
+      <c r="I62" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J62" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E63" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F63" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G63" s="38"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J63" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C64" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D64" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E64" s="38">
+        <v>2.742</v>
+      </c>
+      <c r="F64" s="38">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G64" s="38"/>
+      <c r="H64" s="36"/>
+      <c r="I64" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J64" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D65" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E65" s="38">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="F65" s="38">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="G65" s="38"/>
+      <c r="H65" s="36"/>
+      <c r="I65" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J65" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D66" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" s="38">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="F66" s="38">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G66" s="38"/>
+      <c r="H66" s="36"/>
+      <c r="I66" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J66" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="B67" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C67" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D67" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E67" s="38">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="F67" s="38">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G67" s="38"/>
+      <c r="H67" s="36"/>
+      <c r="I67" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J67" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="B68" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E68" s="38">
+        <v>2.7050000000000001</v>
+      </c>
+      <c r="F68" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G68" s="38"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J68" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B69" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E69" s="38">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="F69" s="38">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G69" s="38"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J69" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E70" s="38">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="F70" s="38">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G70" s="38"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J70" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B71" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E71" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F71" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G71" s="38"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C72" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E72" s="38">
+        <v>2.681</v>
+      </c>
+      <c r="F72" s="38">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="G72" s="38"/>
+      <c r="H72" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="I72" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J72" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B73" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C73" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D73" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E73" s="38">
+        <v>2.762</v>
+      </c>
+      <c r="F73" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G73" s="38"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J73" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C74" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E74" s="38">
+        <v>2.988</v>
+      </c>
+      <c r="F74" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G74" s="38"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J74" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B75" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C75" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E75" s="38">
+        <v>2.7719999999999998</v>
+      </c>
+      <c r="F75" s="38">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G75" s="38"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J75" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B76" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E76" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F76" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G76" s="38"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J76" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C77" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D77" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E77" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F77" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G77" s="38"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J77" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B78" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E78" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F78" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G78" s="38"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J78" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="B79" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E79" s="38">
+        <v>2.7440000000000002</v>
+      </c>
+      <c r="F79" s="38">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="G79" s="38"/>
+      <c r="H79" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="I79" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J79" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C80" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E80" s="38">
+        <v>2.6859999999999999</v>
+      </c>
+      <c r="F80" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G80" s="38"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J80" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E81" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F81" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G81" s="38"/>
+      <c r="H81" s="36"/>
+      <c r="I81" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J81" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C82" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E82" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F82" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G82" s="38"/>
+      <c r="H82" s="36"/>
+      <c r="I82" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J82" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="B83" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C83" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E83" s="38">
+        <v>2.7530000000000001</v>
+      </c>
+      <c r="F83" s="38">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="G83" s="38"/>
+      <c r="H83" s="36"/>
+      <c r="I83" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J83" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C84" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E84" s="38">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="F84" s="38">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G84" s="38"/>
+      <c r="H84" s="36"/>
+      <c r="I84" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J84" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="B85" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E85" s="38">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="F85" s="38">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G85" s="38"/>
+      <c r="H85" s="36"/>
+      <c r="I85" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J85" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E86" s="38">
+        <v>2.681</v>
+      </c>
+      <c r="F86" s="38">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="G86" s="38"/>
+      <c r="H86" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="I86" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J86" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C87" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E87" s="38">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="F87" s="38">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="G87" s="38"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J87" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="B88" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C88" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D88" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E88" s="38">
+        <v>2.5459999999999998</v>
+      </c>
+      <c r="F88" s="38">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G88" s="38"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J88" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B89" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C89" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E89" s="38">
+        <v>2.48</v>
+      </c>
+      <c r="F89" s="38">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="G89" s="38"/>
+      <c r="H89" s="36"/>
+      <c r="I89" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J89" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="B90" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C90" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D90" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="38">
+        <v>1.3</v>
+      </c>
+      <c r="F90" s="38">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="G90" s="38"/>
+      <c r="H90" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I90" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J90" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="B91" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="C91" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E91" s="38">
+        <v>2.8079999999999998</v>
+      </c>
+      <c r="F91" s="38">
+        <v>2.1240000000000001</v>
+      </c>
+      <c r="G91" s="38"/>
+      <c r="H91" s="36"/>
+      <c r="I91" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="J91" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="B92" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C92" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E92" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F92" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G92" s="38"/>
+      <c r="H92" s="36"/>
+      <c r="I92" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J92" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B93" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C93" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D93" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E93" s="38">
+        <v>2.742</v>
+      </c>
+      <c r="F93" s="38">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="G93" s="38"/>
+      <c r="H93" s="36"/>
+      <c r="I93" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J93" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B94" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C94" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D94" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E94" s="38">
+        <v>2.6760000000000002</v>
+      </c>
+      <c r="F94" s="38">
+        <v>1.03E-2</v>
+      </c>
+      <c r="G94" s="38"/>
+      <c r="H94" s="36"/>
+      <c r="I94" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J94" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="B95" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C95" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D95" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E95" s="38">
+        <v>2.742</v>
+      </c>
+      <c r="F95" s="38">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="G95" s="38"/>
+      <c r="H95" s="36"/>
+      <c r="I95" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J95" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B96" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C96" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D96" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E96" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F96" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G96" s="38"/>
+      <c r="H96" s="36"/>
+      <c r="I96" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J96" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="B97" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C97" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D97" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E97" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F97" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G97" s="38"/>
+      <c r="H97" s="36"/>
+      <c r="I97" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J97" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D98" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E98" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F98" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G98" s="38"/>
+      <c r="H98" s="36"/>
+      <c r="I98" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J98" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" s="36" t="s">
+        <v>287</v>
+      </c>
+      <c r="B99" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C99" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D99" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E99" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F99" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G99" s="38"/>
+      <c r="H99" s="36"/>
+      <c r="I99" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J99" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="B100" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C100" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D100" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E100" s="38">
+        <v>2.355</v>
+      </c>
+      <c r="F100" s="38">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="G100" s="38"/>
+      <c r="H100" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="I100" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J100" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="B101" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C101" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D101" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E101" s="38">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="F101" s="38">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G101" s="38"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J101" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="B102" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C102" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D102" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E102" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F102" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G102" s="38"/>
+      <c r="H102" s="36"/>
+      <c r="I102" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J102" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C103" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D103" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E103" s="38">
+        <v>2.7639999999999998</v>
+      </c>
+      <c r="F103" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G103" s="38"/>
+      <c r="H103" s="36"/>
+      <c r="I103" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J103" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B104" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C104" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D104" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E104" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F104" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G104" s="38"/>
+      <c r="H104" s="36"/>
+      <c r="I104" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J104" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="B105" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C105" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D105" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E105" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F105" s="38">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="G105" s="38"/>
+      <c r="H105" s="36"/>
+      <c r="I105" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J105" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="B106" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D106" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E106" s="38">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="F106" s="38">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="G106" s="38"/>
+      <c r="H106" s="36"/>
+      <c r="I106" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J106" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="B107" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C107" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D107" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E107" s="38">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="F107" s="38">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G107" s="38"/>
+      <c r="H107" s="36"/>
+      <c r="I107" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J107" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="B108" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C108" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D108" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E108" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F108" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G108" s="38"/>
+      <c r="H108" s="36"/>
+      <c r="I108" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J108" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="B109" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C109" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D109" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E109" s="38">
+        <v>2.7189999999999999</v>
+      </c>
+      <c r="F109" s="38">
+        <v>2.8E-3</v>
+      </c>
+      <c r="G109" s="38"/>
+      <c r="H109" s="36"/>
+      <c r="I109" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J109" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="B110" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C110" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D110" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E110" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F110" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G110" s="38"/>
+      <c r="H110" s="36"/>
+      <c r="I110" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J110" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="B111" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C111" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D111" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="38">
+        <v>2.37</v>
+      </c>
+      <c r="F111" s="38">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G111" s="38"/>
+      <c r="H111" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I111" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J111" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="B112" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C112" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D112" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E112" s="38">
+        <v>2.5910000000000002</v>
+      </c>
+      <c r="F112" s="38">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G112" s="38"/>
+      <c r="H112" s="36"/>
+      <c r="I112" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J112" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="B113" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C113" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D113" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E113" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F113" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G113" s="38"/>
+      <c r="H113" s="36"/>
+      <c r="I113" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J113" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="B114" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C114" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D114" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E114" s="38">
+        <v>2.9039999999999999</v>
+      </c>
+      <c r="F114" s="38">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="G114" s="38"/>
+      <c r="H114" s="36"/>
+      <c r="I114" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J114" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="B115" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C115" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D115" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E115" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F115" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G115" s="38"/>
+      <c r="H115" s="36"/>
+      <c r="I115" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J115" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="B116" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D116" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E116" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F116" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G116" s="38"/>
+      <c r="H116" s="36"/>
+      <c r="I116" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J116" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="B117" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D117" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E117" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F117" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G117" s="38"/>
+      <c r="H117" s="36"/>
+      <c r="I117" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J117" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="B118" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C118" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D118" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="38">
+        <v>2.4769999999999999</v>
+      </c>
+      <c r="F118" s="38">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="G118" s="38"/>
+      <c r="H118" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I118" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J118" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="B119" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C119" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D119" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E119" s="38">
+        <v>1.54</v>
+      </c>
+      <c r="F119" s="38">
+        <v>5.8884365535558899E-3</v>
+      </c>
+      <c r="G119" s="38">
+        <v>-2.23</v>
+      </c>
+      <c r="H119" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I119" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J119" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B120" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C120" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D120" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E120" s="38">
+        <v>1.54</v>
+      </c>
+      <c r="F120" s="38">
+        <v>5.8884365535558899E-3</v>
+      </c>
+      <c r="G120" s="38">
+        <v>-2.23</v>
+      </c>
+      <c r="H120" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I120" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J120" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A121" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="B121" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C121" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D121" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E121" s="38">
+        <v>2.7530000000000001</v>
+      </c>
+      <c r="F121" s="38">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="G121" s="38"/>
+      <c r="H121" s="36"/>
+      <c r="I121" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J121" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B122" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C122" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D122" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E122" s="38">
+        <v>1.54</v>
+      </c>
+      <c r="F122" s="38">
+        <v>5.8884365535558899E-3</v>
+      </c>
+      <c r="G122" s="38">
+        <v>-2.23</v>
+      </c>
+      <c r="H122" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I122" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J122" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="B123" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C123" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E123" s="38">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="F123" s="38">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G123" s="38"/>
+      <c r="H123" s="36"/>
+      <c r="I123" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J123" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="B124" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C124" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E124" s="38">
+        <v>2.8180000000000001</v>
+      </c>
+      <c r="F124" s="38">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="G124" s="38"/>
+      <c r="H124" s="36"/>
+      <c r="I124" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J124" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="B125" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C125" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D125" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E125" s="38">
+        <v>2.9039999999999999</v>
+      </c>
+      <c r="F125" s="38">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="G125" s="38"/>
+      <c r="H125" s="36"/>
+      <c r="I125" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J125" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="B126" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C126" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D126" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E126" s="38">
+        <v>2.782</v>
+      </c>
+      <c r="F126" s="38">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="G126" s="38"/>
+      <c r="H126" s="36"/>
+      <c r="I126" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J126" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="B127" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C127" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D127" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E127" s="38">
+        <v>2.6859999999999999</v>
+      </c>
+      <c r="F127" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G127" s="38"/>
+      <c r="H127" s="36"/>
+      <c r="I127" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J127" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B128" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C128" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D128" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E128" s="38">
+        <v>2.742</v>
+      </c>
+      <c r="F128" s="38">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G128" s="38"/>
+      <c r="H128" s="36"/>
+      <c r="I128" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J128" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B129" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C129" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D129" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E129" s="38">
+        <v>2.6549999999999998</v>
+      </c>
+      <c r="F129" s="38">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="G129" s="38"/>
+      <c r="H129" s="36"/>
+      <c r="I129" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J129" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="B130" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C130" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D130" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E130" s="38">
+        <v>2.6760000000000002</v>
+      </c>
+      <c r="F130" s="38">
+        <v>1.03E-2</v>
+      </c>
+      <c r="G130" s="38"/>
+      <c r="H130" s="36"/>
+      <c r="I130" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J130" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B131" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C131" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D131" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E131" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F131" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G131" s="38"/>
+      <c r="H131" s="36"/>
+      <c r="I131" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J131" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B132" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C132" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D132" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E132" s="38">
+        <v>1.54</v>
+      </c>
+      <c r="F132" s="38">
+        <v>5.8884365535558899E-3</v>
+      </c>
+      <c r="G132" s="38">
+        <v>-2.23</v>
+      </c>
+      <c r="H132" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I132" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J132" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="B133" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C133" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D133" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E133" s="38">
+        <v>2.5859999999999999</v>
+      </c>
+      <c r="F133" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G133" s="38"/>
+      <c r="H133" s="36"/>
+      <c r="I133" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J133" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="B134" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C134" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D134" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E134" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F134" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G134" s="38"/>
+      <c r="H134" s="36"/>
+      <c r="I134" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J134" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="B135" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C135" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D135" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E135" s="38">
+        <v>2.48</v>
+      </c>
+      <c r="F135" s="38">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="G135" s="38"/>
+      <c r="H135" s="36"/>
+      <c r="I135" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J135" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="B136" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C136" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D136" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E136" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F136" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G136" s="38"/>
+      <c r="H136" s="36"/>
+      <c r="I136" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J136" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B137" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C137" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D137" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E137" s="38">
+        <v>2.7050000000000001</v>
+      </c>
+      <c r="F137" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G137" s="38"/>
+      <c r="H137" s="36"/>
+      <c r="I137" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J137" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="B138" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C138" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D138" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E138" s="38">
+        <v>2.742</v>
+      </c>
+      <c r="F138" s="38">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G138" s="38"/>
+      <c r="H138" s="36"/>
+      <c r="I138" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J138" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="B139" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C139" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D139" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E139" s="38">
+        <v>2.6760000000000002</v>
+      </c>
+      <c r="F139" s="38">
+        <v>1.03E-2</v>
+      </c>
+      <c r="G139" s="38"/>
+      <c r="H139" s="36"/>
+      <c r="I139" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J139" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="B140" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C140" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D140" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E140" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F140" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G140" s="38"/>
+      <c r="H140" s="36"/>
+      <c r="I140" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J140" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B141" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C141" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D141" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="38">
+        <v>2.4769999999999999</v>
+      </c>
+      <c r="F141" s="38">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="G141" s="38"/>
+      <c r="H141" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I141" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J141" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A142" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B142" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C142" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D142" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="38">
+        <v>1.3</v>
+      </c>
+      <c r="F142" s="38">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="G142" s="38"/>
+      <c r="H142" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I142" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J142" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B143" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C143" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D143" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E143" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F143" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G143" s="38"/>
+      <c r="H143" s="36"/>
+      <c r="I143" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J143" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="B144" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C144" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D144" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E144" s="38">
+        <v>1.54</v>
+      </c>
+      <c r="F144" s="38">
+        <v>5.8884365535558899E-3</v>
+      </c>
+      <c r="G144" s="38">
+        <v>-2.23</v>
+      </c>
+      <c r="H144" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I144" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J144" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B145" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C145" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D145" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E145" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F145" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G145" s="38"/>
+      <c r="H145" s="36"/>
+      <c r="I145" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J145" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A146" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="B146" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C146" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D146" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E146" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F146" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G146" s="38"/>
+      <c r="H146" s="36"/>
+      <c r="I146" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J146" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="B147" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C147" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D147" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E147" s="38">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="F147" s="38">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G147" s="38"/>
+      <c r="H147" s="36"/>
+      <c r="I147" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J147" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A148" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="B148" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C148" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D148" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E148" s="38">
+        <v>2.681</v>
+      </c>
+      <c r="F148" s="38">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="G148" s="38"/>
+      <c r="H148" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="I148" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J148" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A149" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="B149" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C149" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D149" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E149" s="38">
+        <v>2.48</v>
+      </c>
+      <c r="F149" s="38">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="G149" s="38"/>
+      <c r="H149" s="36"/>
+      <c r="I149" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J149" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="B150" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C150" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D150" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E150" s="38">
+        <v>1.54</v>
+      </c>
+      <c r="F150" s="38">
+        <v>5.8884365535558899E-3</v>
+      </c>
+      <c r="G150" s="38">
+        <v>-2.23</v>
+      </c>
+      <c r="H150" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I150" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J150" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="B151" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C151" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D151" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E151" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F151" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G151" s="38"/>
+      <c r="H151" s="36"/>
+      <c r="I151" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J151" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="B152" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C152" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D152" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E152" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F152" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G152" s="38"/>
+      <c r="H152" s="36"/>
+      <c r="I152" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J152" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A153" s="35" t="s">
+        <v>205</v>
+      </c>
+      <c r="B153" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C153" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D153" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E153" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F153" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G153" s="38"/>
+      <c r="H153" s="36"/>
+      <c r="I153" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J153" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A154" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="B154" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C154" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D154" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E154" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F154" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G154" s="38"/>
+      <c r="H154" s="36"/>
+      <c r="I154" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J154" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A155" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="B155" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C155" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D155" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E155" s="38">
+        <v>2.649</v>
+      </c>
+      <c r="F155" s="38">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="G155" s="38"/>
+      <c r="H155" s="36"/>
+      <c r="I155" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J155" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A156" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="B156" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C156" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D156" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E156" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F156" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G156" s="38"/>
+      <c r="H156" s="36"/>
+      <c r="I156" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J156" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A157" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="B157" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C157" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D157" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E157" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F157" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G157" s="38"/>
+      <c r="H157" s="36"/>
+      <c r="I157" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J157" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A158" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="B158" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C158" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D158" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E158" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F158" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G158" s="38"/>
+      <c r="H158" s="36"/>
+      <c r="I158" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J158" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A159" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="B159" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C159" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D159" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E159" s="38">
+        <v>2.6549999999999998</v>
+      </c>
+      <c r="F159" s="38">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="G159" s="38"/>
+      <c r="H159" s="36"/>
+      <c r="I159" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J159" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A160" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B160" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C160" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D160" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E160" s="38">
+        <v>2.948</v>
+      </c>
+      <c r="F160" s="38">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G160" s="38"/>
+      <c r="H160" s="36"/>
+      <c r="I160" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J160" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A161" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="B161" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C161" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D161" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E161" s="38">
+        <v>2.879</v>
+      </c>
+      <c r="F161" s="38">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="G161" s="38"/>
+      <c r="H161" s="36"/>
+      <c r="I161" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J161" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A162" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="B162" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C162" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D162" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E162" s="38">
+        <v>2.7050000000000001</v>
+      </c>
+      <c r="F162" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G162" s="38"/>
+      <c r="H162" s="36"/>
+      <c r="I162" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J162" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A163" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B163" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C163" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D163" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E163" s="38">
+        <v>2.7879999999999998</v>
+      </c>
+      <c r="F163" s="38">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="G163" s="38"/>
+      <c r="H163" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="I163" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J163" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A164" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B164" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C164" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D164" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E164" s="38">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="F164" s="38">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G164" s="38"/>
+      <c r="H164" s="36"/>
+      <c r="I164" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J164" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A165" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="B165" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C165" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D165" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E165" s="38">
+        <v>2.6549999999999998</v>
+      </c>
+      <c r="F165" s="38">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="G165" s="38"/>
+      <c r="H165" s="36"/>
+      <c r="I165" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J165" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A166" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="B166" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C166" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D166" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E166" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F166" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G166" s="38"/>
+      <c r="H166" s="36"/>
+      <c r="I166" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J166" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A167" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="B167" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C167" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D167" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E167" s="38">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="F167" s="38">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G167" s="38"/>
+      <c r="H167" s="36"/>
+      <c r="I167" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J167" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A168" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="B168" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C168" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D168" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E168" s="38">
+        <v>2.7719999999999998</v>
+      </c>
+      <c r="F168" s="38">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="G168" s="38"/>
+      <c r="H168" s="36"/>
+      <c r="I168" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J168" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A169" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B169" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C169" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D169" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E169" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F169" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G169" s="38"/>
+      <c r="H169" s="36"/>
+      <c r="I169" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J169" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A170" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="B170" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C170" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D170" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E170" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F170" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G170" s="38"/>
+      <c r="H170" s="36"/>
+      <c r="I170" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J170" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="B171" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C171" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D171" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E171" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F171" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G171" s="38"/>
+      <c r="H171" s="36"/>
+      <c r="I171" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J171" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A172" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="B172" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C172" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D172" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E172" s="38">
+        <v>2.48</v>
+      </c>
+      <c r="F172" s="38">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="G172" s="38"/>
+      <c r="H172" s="36"/>
+      <c r="I172" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J172" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A173" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="B173" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C173" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D173" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E173" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F173" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G173" s="38"/>
+      <c r="H173" s="36"/>
+      <c r="I173" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J173" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A174" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="B174" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C174" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D174" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E174" s="38">
+        <v>2.782</v>
+      </c>
+      <c r="F174" s="38">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="G174" s="38"/>
+      <c r="H174" s="36"/>
+      <c r="I174" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J174" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A175" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="B175" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C175" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D175" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E175" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F175" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G175" s="38"/>
+      <c r="H175" s="36"/>
+      <c r="I175" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J175" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A176" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="B176" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C176" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D176" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E176" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F176" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G176" s="38"/>
+      <c r="H176" s="36"/>
+      <c r="I176" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J176" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A177" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="B177" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C177" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D177" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E177" s="38">
+        <v>2.7050000000000001</v>
+      </c>
+      <c r="F177" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G177" s="38"/>
+      <c r="H177" s="36"/>
+      <c r="I177" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J177" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A178" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="B178" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C178" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D178" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E178" s="38">
+        <v>2.839</v>
+      </c>
+      <c r="F178" s="38">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="G178" s="38"/>
+      <c r="H178" s="36"/>
+      <c r="I178" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J178" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A179" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="B179" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C179" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D179" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E179" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F179" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G179" s="38"/>
+      <c r="H179" s="36"/>
+      <c r="I179" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J179" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A180" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="B180" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C180" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D180" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E180" s="38">
+        <v>2.117</v>
+      </c>
+      <c r="F180" s="38">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="G180" s="38"/>
+      <c r="H180" s="36"/>
+      <c r="I180" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J180" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A181" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="B181" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C181" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D181" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181" s="38">
+        <v>1.3</v>
+      </c>
+      <c r="F181" s="38">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="G181" s="38"/>
+      <c r="H181" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I181" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J181" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A182" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B182" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C182" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D182" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E182" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F182" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G182" s="38"/>
+      <c r="H182" s="36"/>
+      <c r="I182" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J182" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A183" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="B183" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C183" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D183" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E183" s="38">
+        <v>2.875</v>
+      </c>
+      <c r="F183" s="38">
+        <v>5.3E-3</v>
+      </c>
+      <c r="G183" s="38"/>
+      <c r="H183" s="36"/>
+      <c r="I183" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J183" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A184" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="B184" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="C184" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D184" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E184" s="38">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="F184" s="38">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="G184" s="38"/>
+      <c r="H184" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="I184" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J184" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A185" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="B185" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C185" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D185" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E185" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F185" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G185" s="38"/>
+      <c r="H185" s="36"/>
+      <c r="I185" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J185" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A186" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="B186" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C186" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D186" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E186" s="38">
+        <v>2.7050000000000001</v>
+      </c>
+      <c r="F186" s="38">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="G186" s="38"/>
+      <c r="H186" s="36"/>
+      <c r="I186" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J186" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A187" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="B187" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C187" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D187" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E187" s="38">
+        <v>2.8180000000000001</v>
+      </c>
+      <c r="F187" s="38">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="G187" s="38"/>
+      <c r="H187" s="36"/>
+      <c r="I187" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J187" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A188" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="B188" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C188" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D188" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E188" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F188" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G188" s="38"/>
+      <c r="H188" s="36"/>
+      <c r="I188" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J188" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A189" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="B189" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C189" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D189" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E189" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F189" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G189" s="38"/>
+      <c r="H189" s="36"/>
+      <c r="I189" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J189" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A190" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="B190" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C190" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D190" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E190" s="38">
+        <v>2.5859999999999999</v>
+      </c>
+      <c r="F190" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G190" s="38"/>
+      <c r="H190" s="36"/>
+      <c r="I190" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J190" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A191" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="B191" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C191" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D191" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E191" s="38">
+        <v>2.4769999999999999</v>
+      </c>
+      <c r="F191" s="38">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="G191" s="38"/>
+      <c r="H191" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I191" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J191" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A192" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="B192" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C192" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D192" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E192" s="38">
+        <v>2.734</v>
+      </c>
+      <c r="F192" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G192" s="38"/>
+      <c r="H192" s="36"/>
+      <c r="I192" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J192" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A193" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="B193" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C193" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D193" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E193" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F193" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G193" s="38"/>
+      <c r="H193" s="36"/>
+      <c r="I193" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J193" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A194" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B194" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C194" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D194" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E194" s="38">
+        <v>2.734</v>
+      </c>
+      <c r="F194" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G194" s="38"/>
+      <c r="H194" s="36"/>
+      <c r="I194" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J194" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A195" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="B195" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C195" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D195" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E195" s="38">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="F195" s="38">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="G195" s="38"/>
+      <c r="H195" s="36"/>
+      <c r="I195" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J195" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A196" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="B196" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C196" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D196" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E196" s="38">
+        <v>2.91</v>
+      </c>
+      <c r="F196" s="38">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="G196" s="38"/>
+      <c r="H196" s="36"/>
+      <c r="I196" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J196" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A197" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="B197" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="C197" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D197" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E197" s="38">
+        <v>2.37</v>
+      </c>
+      <c r="F197" s="38">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G197" s="38"/>
+      <c r="H197" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I197" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J197" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A198" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="B198" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C198" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D198" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E198" s="38">
+        <v>2.37</v>
+      </c>
+      <c r="F198" s="38">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G198" s="38"/>
+      <c r="H198" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I198" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J198" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A199" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="B199" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C199" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D199" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E199" s="38">
+        <v>2.754</v>
+      </c>
+      <c r="F199" s="38">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="G199" s="38"/>
+      <c r="H199" s="36"/>
+      <c r="I199" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J199" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A200" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="B200" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C200" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D200" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E200" s="38">
+        <v>2.37</v>
+      </c>
+      <c r="F200" s="38">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G200" s="38"/>
+      <c r="H200" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I200" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J200" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A201" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="B201" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C201" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D201" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E201" s="38">
+        <v>2.37</v>
+      </c>
+      <c r="F201" s="38">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G201" s="38"/>
+      <c r="H201" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I201" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J201" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A202" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="B202" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C202" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D202" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E202" s="38">
+        <v>2.9260000000000002</v>
+      </c>
+      <c r="F202" s="38">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="G202" s="38"/>
+      <c r="H202" s="36"/>
+      <c r="I202" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J202" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A203" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="B203" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C203" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D203" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E203" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F203" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G203" s="38"/>
+      <c r="H203" s="36"/>
+      <c r="I203" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J203" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A204" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="B204" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C204" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D204" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E204" s="38">
+        <v>2.7189999999999999</v>
+      </c>
+      <c r="F204" s="38">
+        <v>2.8E-3</v>
+      </c>
+      <c r="G204" s="38"/>
+      <c r="H204" s="36"/>
+      <c r="I204" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J204" s="37" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A205" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="B205" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C205" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D205" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E205" s="38">
+        <v>2.9329999999999998</v>
+      </c>
+      <c r="F205" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G205" s="38"/>
+      <c r="H205" s="36"/>
+      <c r="I205" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J205" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A206" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="B206" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C206" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D206" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E206" s="38">
+        <v>1.3</v>
+      </c>
+      <c r="F206" s="38">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="G206" s="38"/>
+      <c r="H206" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I206" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J206" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A207" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="B207" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C207" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D207" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E207" s="38">
+        <v>1.3</v>
+      </c>
+      <c r="F207" s="38">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="G207" s="38"/>
+      <c r="H207" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I207" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J207" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A208" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="B208" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C208" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D208" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E208" s="38">
+        <v>2.6549999999999998</v>
+      </c>
+      <c r="F208" s="38">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="G208" s="38"/>
+      <c r="H208" s="36"/>
+      <c r="I208" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J208" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A209" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="B209" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C209" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D209" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E209" s="38">
+        <v>2.37</v>
+      </c>
+      <c r="F209" s="38">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G209" s="38"/>
+      <c r="H209" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="I209" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J209" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A210" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="B210" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C210" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D210" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E210" s="38">
+        <v>1.3</v>
+      </c>
+      <c r="F210" s="38">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="G210" s="38"/>
+      <c r="H210" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I210" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J210" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A211" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="B211" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C211" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D211" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E211" s="38">
+        <v>1.3</v>
+      </c>
+      <c r="F211" s="38">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="G211" s="38"/>
+      <c r="H211" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I211" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J211" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A212" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="B212" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C212" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D212" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E212" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F212" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G212" s="38"/>
+      <c r="H212" s="36"/>
+      <c r="I212" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J212" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A213" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="B213" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C213" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="D213" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E213" s="38">
+        <v>1.3</v>
+      </c>
+      <c r="F213" s="38">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="G213" s="38"/>
+      <c r="H213" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I213" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J213" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A214" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B214" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="C214" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="D214" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E214" s="38">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F214" s="38">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="G214" s="38"/>
+      <c r="H214" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="I214" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J214" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A215" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="B215" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C215" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D215" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E215" s="38">
+        <v>2.7879999999999998</v>
+      </c>
+      <c r="F215" s="38">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="G215" s="38"/>
+      <c r="H215" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="I215" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J215" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A216" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="B216" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C216" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D216" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E216" s="38">
+        <v>3.2120000000000002</v>
+      </c>
+      <c r="F216" s="38">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="G216" s="38"/>
+      <c r="H216" s="36"/>
+      <c r="I216" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J216" s="37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A217" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="B217" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C217" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D217" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E217" s="38">
+        <v>1.54</v>
+      </c>
+      <c r="F217" s="38">
+        <v>5.8884365535558899E-3</v>
+      </c>
+      <c r="G217" s="38">
+        <v>-2.23</v>
+      </c>
+      <c r="H217" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I217" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J217" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A218" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="B218" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C218" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D218" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E218" s="38">
+        <v>2.7869999999999999</v>
+      </c>
+      <c r="F218" s="38">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="G218" s="38"/>
+      <c r="H218" s="36"/>
+      <c r="I218" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J218" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A219" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="B219" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C219" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D219" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E219" s="38">
+        <v>2.7869999999999999</v>
+      </c>
+      <c r="F219" s="38">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="G219" s="38"/>
+      <c r="H219" s="36"/>
+      <c r="I219" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J219" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A220" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="B220" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C220" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D220" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E220" s="38">
+        <v>2.7869999999999999</v>
+      </c>
+      <c r="F220" s="38">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="G220" s="38"/>
+      <c r="H220" s="36"/>
+      <c r="I220" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J220" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A221" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="B221" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="C221" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D221" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E221" s="38">
+        <v>2.6</v>
+      </c>
+      <c r="F221" s="38">
+        <v>0.22908676527677729</v>
+      </c>
+      <c r="G221" s="38">
+        <v>-0.64</v>
+      </c>
+      <c r="H221" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="I221" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J221" s="37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A222" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="B222" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C222" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D222" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E222" s="38">
+        <v>2.681</v>
+      </c>
+      <c r="F222" s="38">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="G222" s="38"/>
+      <c r="H222" s="36"/>
+      <c r="I222" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J222" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A223" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="B223" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C223" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D223" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="E223" s="38">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="F223" s="38">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="G223" s="38"/>
+      <c r="H223" s="36"/>
+      <c r="I223" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J223" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A224" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="B224" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="C224" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="D224" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E224" s="38">
+        <v>3.0213333333333332</v>
+      </c>
+      <c r="F224" s="38">
+        <v>6.1400000000000005E-3</v>
+      </c>
+      <c r="G224" s="38"/>
+      <c r="H224" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="I224" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="J224" s="37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A225" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B225" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C225" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D225" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E225" s="42">
+        <v>2.617</v>
+      </c>
+      <c r="F225" s="42">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G225" s="42"/>
+      <c r="H225" s="40"/>
+      <c r="I225" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="J225" s="41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>